--- a/data/data_monitoreo_viviate.xlsx
+++ b/data/data_monitoreo_viviate.xlsx
@@ -447,47 +447,47 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>271</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESPINOZA GUZMAN MAYRA LOURDES</t>
+          <t>CHUNGA DE LA CRUZ ROSA LILIANA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>209</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RUIZ CARRASCO HILLARY SAMANTHA</t>
+          <t>ESPINOZA GUZMAN MAYRA LOURDES</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>204</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FIESTAS PERICHE VIVIANA LISSETH</t>
+          <t>RUIZ CARRASCO HILLARY SAMANTHA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHUNGA DE LA CRUZ ROSA LILIANA</t>
+          <t>FIESTAS PERICHE VIVIANA LISSETH</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>188</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
@@ -497,67 +497,67 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRADO ACARO VANESSA PAOLA</t>
+          <t>PAIVA GARCIA DANIELA MILEYDI</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PALMA CARMENES DE MENA MERCEDES EVERJISTA</t>
+          <t>JIMENEZ GUERRERO JUAN RICARDO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JIMENEZ GUERRERO JUAN RICARDO</t>
+          <t>PAIVA PINDAY ALICIA</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>129</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PAIVA PINDAY ALICIA</t>
+          <t>PRADO ACARO VANESSA PAOLA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>126</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GIRON SILUPU JUAN FRANCISCO</t>
+          <t>PALMA CARMENES DE MENA MERCEDES EVERJISTA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>124</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PAIVA GARCIA DANIELA MILEYDI</t>
+          <t>GIRON SILUPU JUAN FRANCISCO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>116</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_viviate.xlsx
+++ b/data/data_monitoreo_viviate.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>353</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>326</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -527,27 +527,27 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PRADO ACARO VANESSA PAOLA</t>
+          <t>PALMA CARMENES DE MENA MERCEDES EVERJISTA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PALMA CARMENES DE MENA MERCEDES EVERJISTA</t>
+          <t>PRADO ACARO VANESSA PAOLA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_viviate.xlsx
+++ b/data/data_monitoreo_viviate.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>344</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5">
@@ -477,47 +477,47 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FIESTAS PERICHE VIVIANA LISSETH</t>
+          <t>ROSILLO ALBERCA ROXANA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ROSILLO ALBERCA ROXANA</t>
+          <t>FIESTAS PERICHE VIVIANA LISSETH</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAIVA GARCIA DANIELA MILEYDI</t>
+          <t>JIMENEZ GUERRERO JUAN RICARDO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JIMENEZ GUERRERO JUAN RICARDO</t>
+          <t>PAIVA GARCIA DANIELA MILEYDI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>221</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_viviate.xlsx
+++ b/data/data_monitoreo_viviate.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>400</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>369</v>
+        <v>423</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>306</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>298</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>281</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>274</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>239</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>237</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>221</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -537,27 +537,27 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>205</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PRADO ACARO VANESSA PAOLA</t>
+          <t>GIRON SILUPU JUAN FRANCISCO</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>204</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GIRON SILUPU JUAN FRANCISCO</t>
+          <t>PRADO ACARO VANESSA PAOLA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>198</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_viviate.xlsx
+++ b/data/data_monitoreo_viviate.xlsx
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
@@ -517,13 +517,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PAIVA PINDAY ALICIA</t>
+          <t>PALMA CARMENES DE MENA MERCEDES EVERJISTA</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -533,11 +533,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PALMA CARMENES DE MENA MERCEDES EVERJISTA</t>
+          <t>PAIVA PINDAY ALICIA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
